--- a/data/trans_bre/P32C-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,57</t>
+          <t>-2,61; 3,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,96</t>
+          <t>-3,41; -0,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,19</t>
+          <t>-5,26; -0,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 0,32</t>
+          <t>-5,02; 0,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 356,61</t>
+          <t>-100,0; 246,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,76</t>
+          <t>-100,0; 46,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,84</t>
+          <t>-100,0; 85,55</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,28</t>
+          <t>-1,97; 0,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,43</t>
+          <t>-2,41; -0,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,21</t>
+          <t>-1,41; 0,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,78</t>
+          <t>-0,63; 1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,61; 33,06</t>
+          <t>-89,5; 41,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,84; -18,14</t>
+          <t>-100,0; -21,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 41,77</t>
+          <t>-86,2; 68,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 389,47</t>
+          <t>-65,84; 406,4</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,44</t>
+          <t>-3,33; 0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,68</t>
+          <t>-5,08; -0,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,39</t>
+          <t>-2,09; 0,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,16</t>
+          <t>-2,08; 0,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 447,26</t>
+          <t>-100,0; 331,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,04</t>
+          <t>-1,78; 0,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; -0,98</t>
+          <t>-2,46; -1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; -0,37</t>
+          <t>-1,88; -0,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,8</t>
+          <t>-1,06; 0,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,15; 8,69</t>
+          <t>-81,61; 11,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-96,12; -49,87</t>
+          <t>-95,93; -53,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,52; -21,48</t>
+          <t>-88,84; -24,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 90,7</t>
+          <t>-71,05; 70,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32C-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-65,97%</t>
+          <t>-66,76%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,88</t>
+          <t>-2,59; 3,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; -0,94</t>
+          <t>-3,57; -0,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -0,04</t>
+          <t>-5,49; -0,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 0,53</t>
+          <t>-5,09; 0,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,46</t>
+          <t>-100,0; 269,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 46,52</t>
+          <t>-100,0; 98,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,55</t>
+          <t>-100,0; 48,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>171,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,29</t>
+          <t>-1,94; 0,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; -0,49</t>
+          <t>-2,47; -0,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,32</t>
+          <t>-1,39; 0,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,84</t>
+          <t>-0,01; 3,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,5; 41,17</t>
+          <t>-88,09; 44,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,09</t>
+          <t>-100,0; -12,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,2; 68,71</t>
+          <t>-86,63; 61,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,84; 406,4</t>
+          <t>-29,39; 721,32</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-76,12%</t>
+          <t>-79,49%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,38</t>
+          <t>-3,12; 0,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,79</t>
+          <t>-4,91; -0,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,4</t>
+          <t>-2,36; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,16</t>
+          <t>-2,08; 0,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 331,84</t>
+          <t>-100,0; 459,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-24,37%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,06</t>
+          <t>-1,81; 0,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -1,03</t>
+          <t>-2,47; -1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,43</t>
+          <t>-1,8; -0,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,69</t>
+          <t>-0,83; 1,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 11,63</t>
+          <t>-78,91; 16,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-95,93; -53,6</t>
+          <t>-97,27; -55,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,84; -24,08</t>
+          <t>-88,78; -16,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 70,0</t>
+          <t>-59,6; 155,78</t>
         </is>
       </c>
     </row>
